--- a/产品成本测算报价表.xlsx
+++ b/产品成本测算报价表.xlsx
@@ -3086,7 +3086,34 @@
     <t xml:space="preserve">注</t>
   </si>
   <si>
-    <t xml:space="preserve">次日达与特惠普运的目的地划分不同，请选择与所选产品一致的目的地；选错该运费显示空白。</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">物流产品选次日达</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特惠普运；目的地只需填城市名（如“宁波”“杭州”），系统按所选产品自动匹配对应费率行；该产品不覆盖此城市时运费显示空白。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -35434,7 +35461,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -35578,7 +35605,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -36325,7 +36352,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B26" s="18" t="s">
@@ -37148,12 +37175,12 @@
       <formula1>"否,是"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B21" type="list">
-      <formula1>"次日达,特惠普运"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B19:B20" type="list">
+      <formula1>"否,是"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B19:B20" type="list">
-      <formula1>"否,是"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+      <formula1>"次日达,特惠普运"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -39860,7 +39887,7 @@
       <c r="B36" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="54" t="s">
         <v>315</v>
       </c>
     </row>
@@ -39871,7 +39898,7 @@
       <c r="B37" s="10" t="n">
         <v>0.004</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="54" t="s">
         <v>317</v>
       </c>
     </row>
@@ -39882,7 +39909,7 @@
       <c r="B38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="54" t="s">
         <v>319</v>
       </c>
     </row>
@@ -39890,10 +39917,10 @@
       <c r="A39" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="54" t="s">
         <v>321</v>
       </c>
     </row>
@@ -47751,7 +47778,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="72" t="n">
-        <f aca="false">报价汇总!B21</f>
+        <f aca="false">报价汇总!B22</f>
         <v>0</v>
       </c>
     </row>
@@ -47760,7 +47787,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="72" t="n">
-        <f aca="false">报价汇总!B22</f>
+        <f aca="false">报价汇总!B23</f>
         <v>0</v>
       </c>
     </row>
@@ -47769,7 +47796,7 @@
         <v>56</v>
       </c>
       <c r="B6" s="72" t="n">
-        <f aca="false">报价汇总!B23</f>
+        <f aca="false">报价汇总!B24</f>
         <v>0</v>
       </c>
     </row>
@@ -47814,7 +47841,7 @@
         <v>419</v>
       </c>
       <c r="B11" s="72" t="str">
-        <f aca="false">IF(OR(B4="",B5=""),"",B4&amp;"|"&amp;B5)</f>
+        <f aca="false">IF($B$12="","",INDEX(跨越费率!$Q$4:$Q$300,$B$12))</f>
         <v/>
       </c>
     </row>
@@ -47823,7 +47850,7 @@
         <v>673</v>
       </c>
       <c r="B12" s="31" t="str">
-        <f aca="false">IF(B11="","",IFERROR(MATCH(B11,跨越费率!$Q$4:$Q$300,0),""))</f>
+        <f aca="false">IF(OR($B$4="",$B$5=""),"",IFERROR(MATCH(1,INDEX((跨越费率!$A$4:$A$300=$B$4)*(ISNUMBER(SEARCH($B$5,跨越费率!$Q$4:$Q$300))),0),0),""))</f>
         <v/>
       </c>
     </row>
@@ -47925,7 +47952,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="54" t="s">
         <v>683</v>
       </c>
       <c r="B26" s="76" t="n">
@@ -47957,7 +47984,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="54" t="s">
         <v>684</v>
       </c>
       <c r="B27" s="76" t="n">
@@ -48011,7 +48038,7 @@
         <v>686</v>
       </c>
       <c r="B30" s="31" t="n">
-        <f aca="false">报价汇总!B24</f>
+        <f aca="false">报价汇总!B25</f>
         <v>0</v>
       </c>
     </row>
@@ -48043,12 +48070,12 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="54" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="54" t="s">
         <v>691</v>
       </c>
     </row>

--- a/产品成本测算报价表.xlsx
+++ b/产品成本测算报价表.xlsx
@@ -135,7 +135,7 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">珍珠棉</t>
+      <t xml:space="preserve">上下垫片</t>
     </r>
     <r>
       <rPr>
@@ -156,28 +156,28 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">四角护角</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">纸箱</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">护角</t>
     </r>
     <r>
       <rPr>
@@ -12077,6 +12077,44 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">垫片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">护角</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">㎥</t>
     </r>
     <r>
@@ -13211,7 +13249,7 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">单价；</t>
+      <t xml:space="preserve">单价；大板</t>
     </r>
     <r>
       <rPr>
@@ -13221,16 +13259,111 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">EPE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">按体积</t>
+      <t xml:space="preserve">EPE=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上下垫片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×t)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四角护角</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4×t×t×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">体积</t>
     </r>
     <r>
       <rPr>
@@ -36279,7 +36412,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="14" t="str">
-        <f aca="false">IF(OR(B19="是",B20="是"),"自动→大板：EPE珍珠棉+纸箱+护角+托盘+缠绕膜+打包带","自动→小板：防静电气泡袋+隔板+纸箱+护角+托盘+缠绕膜")</f>
+        <f aca="false">IF(OR(B19="是",B20="是"),"自动→大板：EPE上下垫片+四角护角+纸箱+托盘+缠绕膜+打包带","自动→小板：防静电气泡袋+隔板+纸箱+护角+托盘+缠绕膜")</f>
         <v>自动→小板：防静电气泡袋+隔板+纸箱+护角+托盘+缠绕膜</v>
       </c>
       <c r="Z19" s="7" t="s">
@@ -36432,7 +36565,7 @@
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">包装计算!$B$43</f>
-        <v>0.0108</v>
+        <v>0.009</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>71</v>
@@ -36537,7 +36670,7 @@
       </c>
       <c r="B37" s="23" t="n">
         <f aca="false">SUM(B29:B36)*0.15</f>
-        <v>0.0743292</v>
+        <v>0.0740592</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>71</v>
@@ -36555,7 +36688,7 @@
       </c>
       <c r="B38" s="25" t="n">
         <f aca="false">SUM(B29:B37)</f>
-        <v>0.5698572</v>
+        <v>0.5677872</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>71</v>
@@ -36626,7 +36759,7 @@
       </c>
       <c r="B43" s="28" t="n">
         <f aca="false">IFERROR(B38/(1-B42),0)</f>
-        <v>0.670420235294118</v>
+        <v>0.667984941176471</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>71</v>
@@ -36662,7 +36795,7 @@
       </c>
       <c r="B45" s="28" t="n">
         <f aca="false">B43*(1+B44)</f>
-        <v>0.757574865882353</v>
+        <v>0.754822983529412</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>71</v>
@@ -39611,7 +39744,7 @@
         <v>273</v>
       </c>
       <c r="B10" s="50" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>274</v>
@@ -40275,7 +40408,7 @@
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">B22*参数!$B$10</f>
-        <v>0.0108</v>
+        <v>0.009</v>
       </c>
       <c r="C23" s="59"/>
       <c r="D23" s="59"/>
@@ -40298,7 +40431,7 @@
         <v>356</v>
       </c>
       <c r="B25" s="21" t="n">
-        <f aca="false">2*B13*(B4*B5+B4*B6+B5*B6)/10^9</f>
+        <f aca="false">(2*B4*B5*B13+4*B13*B13*B6)/10^9</f>
         <v>0</v>
       </c>
       <c r="C25" s="59"/>
@@ -40323,7 +40456,7 @@
       </c>
       <c r="B27" s="21" t="n">
         <f aca="false">IF($B$9="小板",B23+B24,B26)</f>
-        <v>0.0108</v>
+        <v>0.009</v>
       </c>
       <c r="C27" s="59"/>
       <c r="D27" s="59"/>
@@ -40407,7 +40540,7 @@
       </c>
       <c r="B34" s="64" t="n">
         <f aca="false">B27+B32+B33</f>
-        <v>0.0108</v>
+        <v>0.009</v>
       </c>
       <c r="C34" s="59"/>
       <c r="D34" s="59"/>
@@ -40502,7 +40635,7 @@
       </c>
       <c r="B43" s="64" t="n">
         <f aca="false">B34+IF($B$8="是",B40,0)</f>
-        <v>0.0108</v>
+        <v>0.009</v>
       </c>
       <c r="C43" s="59"/>
       <c r="D43" s="59"/>
@@ -40550,7 +40683,7 @@
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">参数!$B$10</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>380</v>
